--- a/pensum/ok08/OK08_Nullpunktsanalyse_Regneark_Nullpunkt.xlsx
+++ b/pensum/ok08/OK08_Nullpunktsanalyse_Regneark_Nullpunkt.xlsx
@@ -1050,7 +1050,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1209,6 +1209,14 @@
     </xf>
     <xf numFmtId="171" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1521,7 +1529,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
@@ -3096,8 +3104,8 @@
         <v>198</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="21" t="s">
+    <row ht="27" customHeight="true" r="31" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="40" r="A31" t="s">
         <v>199</v>
       </c>
       <c r="B31" s="26" t="n">
@@ -3140,8 +3148,8 @@
         <v>OK — nullpunktet stiger, som det skal når snittprisen faller</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="21" t="s">
+    <row ht="27" customHeight="true" r="37" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="40" r="A37" t="s">
         <v>204</v>
       </c>
       <c r="B37" s="37" t="str">
@@ -3367,8 +3375,8 @@
         <v>227</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="23" t="s">
+    <row ht="27" customHeight="true" r="20" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="41" r="A20" t="s">
         <v>228</v>
       </c>
       <c r="B20" s="30" t="n">
@@ -3513,8 +3521,8 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="23" t="s">
+    <row ht="27" customHeight="true" r="36" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="41" r="A36" t="s">
         <v>247</v>
       </c>
       <c r="B36" s="26" t="n">
